--- a/files/九龙-慈云山、钻石山及新蒲岗-荟淳.xlsx
+++ b/files/九龙-慈云山、钻石山及新蒲岗-荟淳.xlsx
@@ -229,13 +229,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -753,7 +753,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -761,15 +761,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H4" s="5" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>34653</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -803,7 +799,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -811,15 +807,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H5" s="5" t="n">
+        <v>6714000</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>32124</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -1153,7 +1145,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1161,15 +1153,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H12" s="5" t="n">
+        <v>11554000</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>31742</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1203,7 +1191,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1211,15 +1199,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H13" s="5" t="n">
+        <v>6857000</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>33946</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1237,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1261,15 +1245,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H14" s="5" t="n">
+        <v>6571000</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>31440</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1353,7 +1333,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1361,15 +1341,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H16" s="5" t="n">
+        <v>14554000</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>31098</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1517,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1549,15 +1525,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H20" s="5" t="n">
+        <v>11554000</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>30729</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1591,7 +1563,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1599,15 +1571,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H21" s="5" t="n">
+        <v>11269000</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>30959</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1641,7 +1609,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1649,15 +1617,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H22" s="5" t="n">
+        <v>6857000</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>33946</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1691,7 +1655,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1699,15 +1663,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H23" s="5" t="n">
+        <v>6571000</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>31440</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1787,7 +1747,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1795,15 +1755,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H25" s="5" t="n">
+        <v>15554000</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>33667</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2021,7 +1977,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2029,15 +1985,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H30" s="5" t="n">
+        <v>11269000</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>29971</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2071,7 +2023,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2079,15 +2031,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H31" s="5" t="n">
+        <v>11269000</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>30959</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2121,7 +2069,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2129,15 +2077,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H32" s="5" t="n">
+        <v>6857000</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>33946</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2115,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2179,15 +2123,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H33" s="5" t="n">
+        <v>6571000</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>31440</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2207,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2275,15 +2215,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H35" s="5" t="n">
+        <v>15554000</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>33667</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2501,7 +2437,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2509,15 +2445,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H40" s="5" t="n">
+        <v>11269000</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>29971</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2643,7 +2575,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2651,15 +2583,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H43" s="5" t="n">
+        <v>6571000</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>31440</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2969,7 +2897,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -2977,15 +2905,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H50" s="5" t="n">
+        <v>11126000</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>29590</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3249,7 +3173,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -3257,15 +3181,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H56" s="5" t="n">
+        <v>10269000</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>28525</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -3437,7 +3357,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -3445,15 +3365,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H60" s="5" t="n">
+        <v>11126000</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>29590</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4048,10 +3964,10 @@
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>6429000</v>
+        <v>6554000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>30761</v>
+        <v>31359</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -4094,10 +4010,10 @@
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>15497000</v>
+        <v>15697000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>29802</v>
+        <v>30187</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -4140,10 +4056,10 @@
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>14554000</v>
+        <v>14697000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>31502</v>
+        <v>31812</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -7962,10 +7878,10 @@
         </is>
       </c>
       <c r="H158" s="5" t="n">
-        <v>13239000</v>
+        <v>13840000</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>25460</v>
+        <v>26615</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -9871,7 +9787,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>12 套</t>
+          <t>33 套</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
@@ -9886,7 +9802,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>35 套</t>
+          <t>14 套</t>
         </is>
       </c>
     </row>
@@ -10008,20 +9924,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
+$671万
+$32,124/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
+$700万
+$34,653/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L6" s="16" t="inlineStr">
@@ -10039,15 +9955,15 @@
           <t>22/F</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
+$1,155万
+$30,729/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $1,098万
@@ -10055,7 +9971,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $1,055万
@@ -10063,7 +9979,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 356呎 (2房)
 $709万
@@ -10071,12 +9987,12 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>E | 468呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
+$1,455万
+$31,098/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr"/>
@@ -10089,28 +10005,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
+$657万
+$31,440/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
+$686万
+$33,946/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
+$1,155万
+$31,742/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -10120,15 +10036,15 @@
           <t>21/F</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
+$1,127万
+$29,971/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $1,084万
@@ -10136,7 +10052,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $1,055万
@@ -10144,7 +10060,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $699万
@@ -10152,7 +10068,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $701万
@@ -10160,16 +10076,16 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
+$1,555万
+$33,667/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr"/>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $1,678万
@@ -10177,28 +10093,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
+$657万
+$31,440/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
+$686万
+$33,946/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
+$1,127万
+$30,959/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -10208,15 +10124,15 @@
           <t>20/F</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
+$1,127万
+$29,971/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $1,084万
@@ -10224,7 +10140,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $1,041万
@@ -10232,7 +10148,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $699万
@@ -10240,7 +10156,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $709万
@@ -10248,16 +10164,16 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
+$1,555万
+$33,667/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $1,653万
@@ -10265,28 +10181,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
+$657万
+$31,440/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
+$686万
+$33,946/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
+$1,127万
+$30,959/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -10296,15 +10212,15 @@
           <t>19/F</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
+$1,113万
+$29,590/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $1,070万
@@ -10312,7 +10228,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $1,041万
@@ -10320,7 +10236,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $699万
@@ -10328,7 +10244,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $709万
@@ -10336,7 +10252,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
 $1,498万
@@ -10345,7 +10261,7 @@
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $1,627万
@@ -10353,15 +10269,15 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="18" t="inlineStr">
+$657万
+$31,440/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K10" s="19" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $671万
@@ -10369,7 +10285,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L10" s="19" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $1,098万
@@ -10384,15 +10300,15 @@
           <t>18/F</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
+$1,113万
+$29,590/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $726万
@@ -10400,7 +10316,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $1,013万
@@ -10408,7 +10324,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $681万
@@ -10416,15 +10332,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
+$1,027万
+$28,525/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
 $1,484万
@@ -10433,7 +10349,7 @@
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr"/>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $1,601万
@@ -10441,7 +10357,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $450万
@@ -10449,7 +10365,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="K11" s="18" t="inlineStr">
+      <c r="K11" s="19" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $671万
@@ -10457,7 +10373,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="19" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $1,098万
@@ -10472,7 +10388,7 @@
           <t>17/F</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $737万
@@ -10480,7 +10396,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $1,041万
@@ -10488,7 +10404,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $1,013万
@@ -10496,7 +10412,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $689万
@@ -10504,7 +10420,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $699万
@@ -10512,7 +10428,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
 $999万
@@ -10521,7 +10437,7 @@
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr"/>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $1,575万
@@ -10529,7 +10445,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="J12" s="19" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $643万
@@ -10537,7 +10453,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="K12" s="18" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $671万
@@ -10545,7 +10461,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L12" s="18" t="inlineStr">
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $1,070万
@@ -10560,7 +10476,7 @@
           <t>16/F</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $737万
@@ -10568,7 +10484,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $1,041万
@@ -10576,7 +10492,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $699万
@@ -10584,7 +10500,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $689万
@@ -10592,7 +10508,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $998万
@@ -10600,24 +10516,112 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
-$1,455万
-$31,502/呎
+$1,470万
+$31,812/呎
 (在售)</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr"/>
-      <c r="I13" s="20" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
-$1,550万
-$29,802/呎
+$1,570万
+$30,187/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$655万
+$31,359/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$657万
+$32,530/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$1,070万
+$29,387/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>15/F</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$720万
+$19,136/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$1,041万
+$29,327/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$998万
+$28,361/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$666万
+$18,500/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$670万
+$18,617/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>F | 462呎 (3房)
+$1,441万
+$31,193/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr"/>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1,524万
+$29,308/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $643万
@@ -10625,7 +10629,183 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K13" s="20" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$460万
+$22,772/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$724万
+$19,904/呎
+(已售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>12/F</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$1,041万
+$27,689/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$706万
+$19,887/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$674万
+$19,156/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$661万
+$18,356/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$665万
+$18,475/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>F | 462呎 (3房)
+$1,427万
+$30,885/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr"/>
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1,498万
+$28,813/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$440万
+$21,053/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$657万
+$32,530/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$729万
+$20,022/呎
+(已售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>11/F</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$712万
+$18,941/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$719万
+$20,248/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$667万
+$18,952/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$656万
+$18,214/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$660万
+$18,331/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>F | 461呎 (3房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 519呎 (3房)
+$995万
+$19,168/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$643万
+$30,761/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $657万
@@ -10633,110 +10813,22 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="L16" s="19" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
-$1,070万
-$29,387/呎
+$1,055万
+$28,995/呎
 (在售)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$720万
-$19,136/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$1,041万
-$29,327/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$998万
-$28,361/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$666万
-$18,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$670万
-$18,617/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 462呎 (3房)
-$1,441万
-$31,193/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr"/>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1,524万
-$29,308/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$643万
-$30,761/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K14" s="19" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$460万
-$22,772/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$724万
-$19,904/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>10/F</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $1,041万
@@ -10744,183 +10836,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$706万
-$19,887/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$674万
-$19,156/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$661万
-$18,356/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$665万
-$18,475/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 462呎 (3房)
-$1,427万
-$30,885/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr"/>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1,498万
-$28,813/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J15" s="19" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$440万
-$21,053/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$657万
-$32,530/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$729万
-$20,022/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$712万
-$18,941/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$719万
-$20,248/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$667万
-$18,952/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$656万
-$18,214/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$660万
-$18,331/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr"/>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>H | 519呎 (3房)
-$995万
-$19,168/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$643万
-$30,761/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K16" s="20" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$657万
-$32,530/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L16" s="18" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$1,055万
-$28,995/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$1,041万
-$27,689/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $692万
@@ -10928,7 +10844,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $660万
@@ -10936,7 +10852,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $650万
@@ -10944,7 +10860,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $655万
@@ -10952,7 +10868,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $638万
@@ -10960,7 +10876,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H17" s="18" t="inlineStr">
         <is>
           <t>G | 432呎 (3房)
 $1,313万
@@ -10968,7 +10884,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $982万
@@ -10976,7 +10892,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J17" s="18" t="inlineStr">
+      <c r="J17" s="19" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $629万
@@ -10984,7 +10900,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K17" s="18" t="inlineStr">
+      <c r="K17" s="19" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $643万
@@ -10992,7 +10908,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L17" s="19" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $719万
@@ -11007,7 +10923,7 @@
           <t>9/F</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $709万
@@ -11015,7 +10931,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $685万
@@ -11023,7 +10939,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $653万
@@ -11031,7 +10947,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $643万
@@ -11039,7 +10955,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $648万
@@ -11047,7 +10963,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $631万
@@ -11055,7 +10971,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>G | 432呎 (3房)
 $1,284万
@@ -11063,7 +10979,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $950万
@@ -11071,7 +10987,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $429万
@@ -11079,7 +10995,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K18" s="18" t="inlineStr">
+      <c r="K18" s="19" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $643万
@@ -11087,7 +11003,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L18" s="19" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $719万
@@ -11102,7 +11018,7 @@
           <t>8/F</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $1,013万
@@ -11110,7 +11026,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $678万
@@ -11118,7 +11034,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $648万
@@ -11126,7 +11042,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $636万
@@ -11134,7 +11050,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $643万
@@ -11142,7 +11058,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $624万
@@ -11150,7 +11066,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="H19" s="18" t="inlineStr">
         <is>
           <t>G | 432呎 (3房)
 $1,270万
@@ -11158,7 +11074,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $941万
@@ -11166,7 +11082,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J19" s="19" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $429万
@@ -11174,7 +11090,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K19" s="20" t="inlineStr">
+      <c r="K19" s="18" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $643万
@@ -11182,7 +11098,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L19" s="19" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $688万
@@ -11197,7 +11113,7 @@
           <t>7/F</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $1,013万
@@ -11205,7 +11121,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $670万
@@ -11213,7 +11129,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $641万
@@ -11221,7 +11137,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $629万
@@ -11229,7 +11145,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $636万
@@ -11237,7 +11153,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $617万
@@ -11245,7 +11161,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 432呎 (3房)
 $849万
@@ -11253,7 +11169,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $934万
@@ -11261,7 +11177,7 @@
 (26年-07月)</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $429万
@@ -11269,7 +11185,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K20" s="18" t="inlineStr">
+      <c r="K20" s="19" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $629万
@@ -11277,7 +11193,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L20" s="19" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $682万
@@ -11292,7 +11208,7 @@
           <t>6/F</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $690万
@@ -11300,7 +11216,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $663万
@@ -11308,7 +11224,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $634万
@@ -11316,7 +11232,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $622万
@@ -11324,7 +11240,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $628万
@@ -11332,7 +11248,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $610万
@@ -11340,7 +11256,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 432呎 (3房)
 $836万
@@ -11348,15 +11264,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="18" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
-$1,324万
-$25,460/呎
+$1,384万
+$26,615/呎
 (在售)</t>
         </is>
       </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $409万
@@ -11364,7 +11280,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K21" s="19" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $420万
@@ -11372,7 +11288,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L21" s="19" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $677万
@@ -11387,7 +11303,7 @@
           <t>5/F</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $998万
@@ -11395,7 +11311,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $656万
@@ -11403,7 +11319,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $626万
@@ -11411,7 +11327,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $615万
@@ -11419,7 +11335,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $621万
@@ -11427,7 +11343,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $603万
@@ -11435,7 +11351,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="18" t="inlineStr">
+      <c r="H22" s="19" t="inlineStr">
         <is>
           <t>G | 432呎 (3房)
 $1,184万
@@ -11443,7 +11359,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $899万
@@ -11451,7 +11367,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $399万
@@ -11459,7 +11375,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K22" s="19" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $409万
@@ -11467,7 +11383,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L22" s="19" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $674万
@@ -11482,7 +11398,7 @@
           <t>3/F</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $998万
@@ -11490,7 +11406,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $659万
@@ -11498,7 +11414,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $619万
@@ -11506,7 +11422,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $607万
@@ -11514,7 +11430,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $614万
@@ -11522,7 +11438,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $595万
@@ -11546,7 +11462,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $399万
@@ -11554,7 +11470,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K23" s="19" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $409万
@@ -11562,7 +11478,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L23" s="19" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $668万
@@ -11585,7 +11501,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $659万
@@ -11593,7 +11509,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $612万
@@ -11601,7 +11517,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $579万
@@ -11609,7 +11525,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $607万
@@ -11617,7 +11533,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $588万
@@ -11634,7 +11550,7 @@
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr"/>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $399万
@@ -11642,7 +11558,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K24" s="18" t="inlineStr">
+      <c r="K24" s="19" t="inlineStr">
         <is>
           <t>K | 200呎 (开放式)
 $614万

--- a/files/九龙-慈云山、钻石山及新蒲岗-荟淳.xlsx
+++ b/files/九龙-慈云山、钻石山及新蒲岗-荟淳.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="荟淳 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1384,7 +1245,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1798,7 +1659,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1844,7 +1705,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2258,7 +2119,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2304,7 +2165,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2764,7 +2625,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3224,7 +3085,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3316,7 +3177,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3592,7 +3453,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3638,7 +3499,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3684,7 +3545,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3822,7 +3683,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4144,7 +4005,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4328,7 +4189,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4558,7 +4419,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4604,7 +4465,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4742,7 +4603,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4788,7 +4649,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4880,7 +4741,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5018,7 +4879,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5064,7 +4925,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5110,7 +4971,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5156,7 +5017,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5386,7 +5247,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5482,7 +5343,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5528,7 +5389,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5574,7 +5435,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5620,7 +5481,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5666,7 +5527,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5712,7 +5573,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5850,7 +5711,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5942,7 +5803,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -5988,7 +5849,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6034,7 +5895,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6080,7 +5941,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6126,7 +5987,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6218,7 +6079,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6310,7 +6171,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6356,7 +6217,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6448,7 +6309,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6494,7 +6355,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6540,7 +6401,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6586,7 +6447,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6632,7 +6493,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6724,7 +6585,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6816,7 +6677,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6862,7 +6723,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6954,7 +6815,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7000,7 +6861,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7046,7 +6907,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7092,7 +6953,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7138,7 +6999,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7230,7 +7091,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7322,7 +7183,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7414,7 +7275,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7460,7 +7321,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7506,7 +7367,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7552,7 +7413,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7598,7 +7459,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7644,7 +7505,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7736,7 +7597,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7782,7 +7643,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7828,7 +7689,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7920,7 +7781,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7966,7 +7827,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8012,7 +7873,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8058,7 +7919,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8104,7 +7965,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8150,7 +8011,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8196,7 +8057,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8242,7 +8103,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8288,7 +8149,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8334,7 +8195,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8380,7 +8241,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8472,7 +8333,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8518,7 +8379,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8564,7 +8425,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8610,7 +8471,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8656,7 +8517,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8748,7 +8609,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8794,7 +8655,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8840,7 +8701,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8986,7 +8847,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9032,7 +8893,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9078,7 +8939,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9124,7 +8985,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9170,7 +9031,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9358,7 +9219,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9454,7 +9315,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9500,7 +9361,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9546,7 +9407,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9592,7 +9453,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9638,7 +9499,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9710,1876 +9571,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>荟淳 - 荟淳 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>195 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>48 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>33 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>100 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>14 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 472呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 679呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$671万
-$32,124/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$700万
-$34,653/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$1,155万
-$30,729/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$1,098万
-$30,938/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$1,055万
-$29,983/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>D | 356呎 (2房)
-$709万
-$19,910/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 468呎 (3房)
-$1,455万
-$31,098/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 666呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$657万
-$31,440/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$686万
-$33,946/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$1,155万
-$31,742/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$1,127万
-$29,971/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$1,084万
-$30,535/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$1,055万
-$29,983/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$699万
-$19,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$701万
-$19,469/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 462呎 (3房)
-$1,555万
-$33,667/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr"/>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1,678万
-$32,275/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$657万
-$31,440/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$686万
-$33,946/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$1,127万
-$30,959/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$1,127万
-$29,971/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$1,084万
-$30,535/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$1,041万
-$29,577/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$699万
-$19,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$709万
-$19,689/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 462呎 (3房)
-$1,555万
-$33,667/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr"/>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1,653万
-$31,781/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$657万
-$31,440/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K9" s="18" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$686万
-$33,946/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L9" s="18" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$1,127万
-$30,959/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$1,113万
-$29,590/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$1,070万
-$30,132/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$1,041万
-$29,577/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$699万
-$19,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$709万
-$19,689/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>F | 462呎 (3房)
-$1,498万
-$32,431/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr"/>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1,627万
-$31,287/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$657万
-$31,440/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K10" s="19" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$671万
-$33,238/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L10" s="19" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$1,098万
-$30,173/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$1,113万
-$29,590/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$726万
-$20,445/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$1,013万
-$28,767/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$681万
-$18,925/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$1,027万
-$28,525/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>F | 462呎 (3房)
-$1,484万
-$32,121/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr"/>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1,601万
-$30,790/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$450万
-$21,531/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K11" s="19" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$671万
-$33,238/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L11" s="19" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$1,098万
-$30,173/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$737万
-$19,596/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$1,041万
-$29,327/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$1,013万
-$28,767/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$689万
-$19,133/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$699万
-$19,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>F | 462呎 (3房)
-$999万
-$21,619/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr"/>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1,575万
-$30,296/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$643万
-$30,761/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$671万
-$33,238/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$1,070万
-$29,387/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$737万
-$19,596/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$1,041万
-$29,327/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$699万
-$19,852/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$689万
-$19,133/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$998万
-$27,731/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>F | 462呎 (3房)
-$1,470万
-$31,812/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr"/>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1,570万
-$30,187/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$655万
-$31,359/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$657万
-$32,530/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$1,070万
-$29,387/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$720万
-$19,136/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$1,041万
-$29,327/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$998万
-$28,361/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$666万
-$18,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$670万
-$18,617/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>F | 462呎 (3房)
-$1,441万
-$31,193/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr"/>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1,524万
-$29,308/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J14" s="19" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$643万
-$30,761/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K14" s="20" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$460万
-$22,772/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$724万
-$19,904/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$1,041万
-$27,689/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$706万
-$19,887/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$674万
-$19,156/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$661万
-$18,356/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$665万
-$18,475/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="19" t="inlineStr">
-        <is>
-          <t>F | 462呎 (3房)
-$1,427万
-$30,885/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr"/>
-      <c r="I15" s="19" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1,498万
-$28,813/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$440万
-$21,053/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K15" s="19" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$657万
-$32,530/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L15" s="20" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$729万
-$20,022/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$712万
-$18,941/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$719万
-$20,248/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$667万
-$18,952/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$656万
-$18,214/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$660万
-$18,331/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr"/>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t>H | 519呎 (3房)
-$995万
-$19,168/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="19" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$643万
-$30,761/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K16" s="18" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$657万
-$32,530/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L16" s="19" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$1,055万
-$28,995/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$1,041万
-$27,689/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$692万
-$19,487/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$660万
-$18,747/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$650万
-$18,069/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$655万
-$18,189/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$638万
-$18,724/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 432呎 (3房)
-$1,313万
-$30,384/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$982万
-$18,888/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J17" s="19" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$629万
-$30,077/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K17" s="19" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$643万
-$31,827/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$719万
-$19,747/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$709万
-$18,851/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$685万
-$19,287/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$653万
-$18,545/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$643万
-$17,872/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$648万
-$17,989/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$631万
-$18,516/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 432呎 (3房)
-$1,284万
-$29,722/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$950万
-$18,260/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="20" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$429万
-$20,517/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K18" s="19" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$643万
-$31,827/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$719万
-$19,747/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$1,013万
-$26,931/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$678万
-$19,087/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$648万
-$18,409/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$636万
-$17,669/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$643万
-$17,858/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$624万
-$18,305/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 432呎 (3房)
-$1,270万
-$29,391/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$941万
-$18,104/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="20" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$429万
-$20,517/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K19" s="18" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$643万
-$31,827/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L19" s="20" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$688万
-$18,904/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$1,013万
-$26,931/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$670万
-$18,887/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$641万
-$18,205/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$629万
-$17,469/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$636万
-$17,658/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$617万
-$18,091/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>G | 432呎 (3房)
-$849万
-$19,650/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$934万
-$17,965/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$429万
-$20,517/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K20" s="19" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$629万
-$31,119/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L20" s="20" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$682万
-$18,750/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$690万
-$18,340/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$663万
-$18,687/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$634万
-$18,003/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$622万
-$17,272/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$628万
-$17,458/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$610万
-$17,880/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>G | 432呎 (3房)
-$836万
-$19,363/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1,384万
-$26,615/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$409万
-$19,560/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K21" s="20" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$420万
-$20,792/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L21" s="20" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$677万
-$18,596/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$998万
-$26,551/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$656万
-$18,487/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$626万
-$17,795/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$615万
-$17,072/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$621万
-$17,258/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$603万
-$17,672/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>G | 432呎 (3房)
-$1,184万
-$27,407/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$899万
-$17,285/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="20" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$399万
-$19,081/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K22" s="20" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$409万
-$20,238/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L22" s="20" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$674万
-$18,514/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$998万
-$26,551/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$659万
-$18,558/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$619万
-$17,591/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$607万
-$16,869/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$614万
-$17,058/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$595万
-$17,460/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 433呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 481呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="20" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$399万
-$19,081/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K23" s="20" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$409万
-$20,238/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L23" s="20" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$668万
-$18,360/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 337呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$659万
-$18,558/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$612万
-$17,389/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$579万
-$16,078/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$607万
-$16,858/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$588万
-$17,246/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 400呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$399万
-$19,081/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K24" s="19" t="inlineStr">
-        <is>
-          <t>K | 200呎 (开放式)
-$614万
-$30,715/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L24" s="16" t="inlineStr">
-        <is>
-          <t>L | 324呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-慈云山、钻石山及新蒲岗-荟淳.xlsx
+++ b/files/九龙-慈云山、钻石山及新蒲岗-荟淳.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="荟淳" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,101 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +147,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +228,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +661,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -9571,4 +9758,1876 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>荟淳 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 472呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 679呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$671万
+$32,124/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$700万
+$34,653/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$1155万
+$30,729/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$1098万
+$30,938/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$1055万
+$29,983/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>D | 356呎 (2房)
+$709万
+$19,910/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 468呎 (3房)
+$1455万
+$31,098/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 666呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$657万
+$31,440/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$686万
+$33,946/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$1155万
+$31,742/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$1127万
+$29,971/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$1084万
+$30,535/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$1055万
+$29,983/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$699万
+$19,411/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$701万
+$19,469/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 462呎 (3房)
+$1555万
+$33,667/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr"/>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1678万
+$32,275/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$657万
+$31,440/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$686万
+$33,946/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L7" s="22" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$1127万
+$30,959/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$1127万
+$29,971/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$1084万
+$30,535/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$1041万
+$29,577/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$699万
+$19,411/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$709万
+$19,689/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 462呎 (3房)
+$1555万
+$33,667/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr"/>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1653万
+$31,781/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$657万
+$31,440/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$686万
+$33,946/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$1127万
+$30,959/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$1113万
+$29,590/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$1070万
+$30,132/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$1041万
+$29,577/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$699万
+$19,411/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$709万
+$19,689/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>F | 462呎 (3房)
+$1498万
+$32,431/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr"/>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1627万
+$31,287/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$657万
+$31,440/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$671万
+$33,238/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$1098万
+$30,173/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$1113万
+$29,590/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$726万
+$20,445/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$1013万
+$28,767/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$681万
+$18,925/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$1027万
+$28,525/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>F | 462呎 (3房)
+$1484万
+$32,121/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr"/>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1601万
+$30,790/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J10" s="24" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$450万
+$21,531/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$671万
+$33,238/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$1098万
+$30,173/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$737万
+$19,596/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$1041万
+$29,327/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$1013万
+$28,767/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$689万
+$19,133/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$699万
+$19,411/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>F | 462呎 (3房)
+$999万
+$21,619/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr"/>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1575万
+$30,296/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$643万
+$30,761/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$671万
+$33,238/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$1070万
+$29,387/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$737万
+$19,596/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$1041万
+$29,327/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$699万
+$19,852/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$689万
+$19,133/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$998万
+$27,731/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>F | 462呎 (3房)
+$1470万
+$31,812/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr"/>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1570万
+$30,187/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$655万
+$31,359/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$657万
+$32,530/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$1070万
+$29,387/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$720万
+$19,136/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$1041万
+$29,327/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$998万
+$28,361/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$666万
+$18,500/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$670万
+$18,617/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>F | 462呎 (3房)
+$1441万
+$31,193/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr"/>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1524万
+$29,308/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$643万
+$30,761/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$460万
+$22,772/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L13" s="24" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$724万
+$19,904/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$1041万
+$27,689/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$706万
+$19,887/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$674万
+$19,156/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$661万
+$18,356/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$665万
+$18,475/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>F | 462呎 (3房)
+$1427万
+$30,885/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr"/>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1498万
+$28,813/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$440万
+$21,053/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$657万
+$32,530/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$729万
+$20,022/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$712万
+$18,941/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$719万
+$20,248/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$667万
+$18,952/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$656万
+$18,214/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$660万
+$18,331/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr"/>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>H | 519呎 (3房)
+$995万
+$19,168/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$643万
+$30,761/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$657万
+$32,530/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$1055万
+$28,995/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$1041万
+$27,689/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$692万
+$19,487/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$660万
+$18,747/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$650万
+$18,069/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$655万
+$18,189/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$638万
+$18,724/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 432呎 (3房)
+$1313万
+$30,384/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$982万
+$18,888/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$629万
+$30,077/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$643万
+$31,827/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L16" s="24" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$719万
+$19,747/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$709万
+$18,851/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$685万
+$19,287/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$653万
+$18,545/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$643万
+$17,872/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$648万
+$17,989/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$631万
+$18,516/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 432呎 (3房)
+$1284万
+$29,722/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$950万
+$18,260/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$429万
+$20,517/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$643万
+$31,827/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L17" s="24" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$719万
+$19,747/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$1013万
+$26,931/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$678万
+$19,087/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$648万
+$18,409/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$636万
+$17,669/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$643万
+$17,858/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$624万
+$18,305/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 432呎 (3房)
+$1270万
+$29,391/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$941万
+$18,104/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J18" s="24" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$429万
+$20,517/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$643万
+$31,827/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L18" s="24" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$688万
+$18,904/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$1013万
+$26,931/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$670万
+$18,887/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$641万
+$18,205/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$629万
+$17,469/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$636万
+$17,658/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$617万
+$18,091/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>G | 432呎 (3房)
+$849万
+$19,650/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$934万
+$17,965/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$429万
+$20,517/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K19" s="23" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$629万
+$31,119/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L19" s="24" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$682万
+$18,750/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$690万
+$18,340/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$663万
+$18,687/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$634万
+$18,003/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$622万
+$17,272/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$628万
+$17,458/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$610万
+$17,880/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>G | 432呎 (3房)
+$836万
+$19,363/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1384万
+$26,615/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J20" s="24" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$409万
+$19,560/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$420万
+$20,792/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$677万
+$18,596/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$998万
+$26,551/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$656万
+$18,487/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$626万
+$17,795/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$615万
+$17,072/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$621万
+$17,258/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$603万
+$17,672/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>G | 432呎 (3房)
+$1184万
+$27,407/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$899万
+$17,285/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J21" s="24" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$399万
+$19,081/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$409万
+$20,238/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L21" s="24" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$674万
+$18,514/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$998万
+$26,551/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$659万
+$18,558/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$619万
+$17,591/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$607万
+$16,869/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$614万
+$17,058/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$595万
+$17,460/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 433呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 481呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$399万
+$19,081/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$409万
+$20,238/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L22" s="24" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$668万
+$18,360/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 337呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$659万
+$18,558/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$612万
+$17,389/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$579万
+$16,078/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$607万
+$16,858/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$588万
+$17,246/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 400呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr"/>
+      <c r="J23" s="24" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$399万
+$19,081/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>K | 200呎 (开放式)
+$614万
+$30,715/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>L | 324呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-慈云山、钻石山及新蒲岗-荟淳.xlsx
+++ b/files/九龙-慈云山、钻石山及新蒲岗-荟淳.xlsx
@@ -661,7 +661,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-慈云山、钻石山及新蒲岗-荟淳.xlsx
+++ b/files/九龙-慈云山、钻石山及新蒲岗-荟淳.xlsx
@@ -121,11 +121,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -133,6 +128,11 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -277,13 +277,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:N197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -664,6 +664,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -721,6 +725,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -771,6 +795,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -801,7 +845,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -817,6 +861,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>24257</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -847,7 +907,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -863,6 +923,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>4699800</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>22487</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -913,6 +989,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -963,6 +1059,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1013,6 +1129,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1063,6 +1199,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1113,6 +1269,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1163,6 +1339,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1193,7 +1389,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1209,6 +1405,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>8087800</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>22219</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1239,7 +1451,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1255,6 +1467,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>4799900</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>23762</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1285,7 +1513,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1301,6 +1529,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>4599700</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>22008</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1351,6 +1595,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1381,7 +1645,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1397,6 +1661,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>10187800</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>21769</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1443,6 +1723,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>7088000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>19910</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1489,6 +1785,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7387800</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>20988</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1535,6 +1847,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>7688100</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>21657</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1565,7 +1893,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1581,6 +1909,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>8087800</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>21510</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1611,7 +1955,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1627,6 +1971,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>7888300</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>21671</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1673,6 +2033,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>4799900</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>23762</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1719,6 +2095,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>4599700</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>22008</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1765,6 +2157,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>11748100</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>22592</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1795,7 +2203,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1811,6 +2219,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>10887800</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>23567</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1857,6 +2281,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>7009000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>19469</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1903,6 +2343,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>6988000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>19411</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1949,6 +2405,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>7387800</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>20988</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1995,6 +2467,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>7588000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>21375</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2025,7 +2513,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2041,6 +2529,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>7888300</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>20980</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2071,7 +2575,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2087,6 +2591,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>7888300</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>21671</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2133,6 +2653,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>4799900</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>23762</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2179,6 +2715,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>4599700</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>22008</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2209,7 +2761,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2225,6 +2777,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>11568200</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>22247</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2255,7 +2823,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2271,6 +2839,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>10887800</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>23567</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2317,6 +2901,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>7088000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>19689</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2363,6 +2963,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>6988000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>19411</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2409,6 +3025,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>7287700</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>20704</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2455,6 +3087,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>7588000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>21375</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2485,7 +3133,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2501,6 +3149,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>7888300</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>20980</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2547,6 +3211,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>7688100</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>21121</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2593,6 +3273,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>4699800</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>23266</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2639,6 +3335,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>4599700</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>22008</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2669,7 +3381,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2685,6 +3397,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>11388300</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>21901</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2731,6 +3459,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>10488100</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>22702</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2777,6 +3521,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>7088000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>19689</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2823,6 +3583,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>6988000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>19411</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2869,6 +3645,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>7287700</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>20704</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2915,6 +3707,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>7487900</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>21093</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2945,7 +3753,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -2961,6 +3769,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>7788200</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>20713</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3007,6 +3831,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>7688100</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>21121</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3053,6 +3893,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>4699800</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>23266</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3099,6 +3955,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>21531</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3129,7 +4001,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -3145,6 +4017,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>11207700</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>21553</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3191,6 +4079,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>10388000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>22485</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3221,7 +4125,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -3237,6 +4141,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>7188300</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>19968</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3283,6 +4203,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>6813000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>18925</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3329,6 +4265,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>7088200</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>20137</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3375,6 +4327,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>7258000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>20445</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3405,7 +4373,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -3421,6 +4389,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>7788200</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>20713</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3467,6 +4451,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>7487900</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>20571</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3513,6 +4513,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>4699800</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>23266</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3559,6 +4575,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>4500300</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>21533</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3605,6 +4637,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>11027800</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>21207</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3651,6 +4699,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>9988000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>21619</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3697,6 +4761,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>6988000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>19411</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3743,6 +4823,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>6888000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>19133</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3789,6 +4885,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>7088200</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>20137</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3835,6 +4947,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>7287700</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>20529</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3881,6 +5009,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>7368000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>19596</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3927,6 +5071,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>7487900</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>20571</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3973,6 +5133,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>4599700</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>22771</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4019,6 +5195,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>4587800</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>21951</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4065,6 +5257,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>10987900</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>21131</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4111,6 +5319,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>10287900</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>22268</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4157,6 +5381,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>6988100</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>19411</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4203,6 +5443,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>6888000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>19133</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4249,6 +5505,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>6988000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>19852</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4295,6 +5567,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>7287700</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>20529</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4341,6 +5629,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>7368000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>19596</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4387,6 +5691,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>7245000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>19904</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4433,6 +5753,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>22772</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4479,6 +5815,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>4500300</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>21533</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4509,7 +5861,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -4525,6 +5877,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>10668000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>20515</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4571,6 +5939,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>10087700</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>21835</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4617,6 +6001,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>6702000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>18617</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4663,6 +6063,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>6660000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>18500</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4709,6 +6125,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>6988100</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>19853</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4755,6 +6187,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>7287700</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>20529</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4801,6 +6249,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>7195000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>19136</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4847,6 +6311,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>7288000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>20022</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4893,6 +6373,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>4599700</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>22771</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4939,6 +6435,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>21053</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4985,6 +6497,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>10488100</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>20169</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5031,6 +6559,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>9988300</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>21620</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5077,6 +6621,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>6651000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>18475</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5123,6 +6683,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>6608000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>18356</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5169,6 +6745,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>6743000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>19156</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5215,6 +6807,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>7060000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>19887</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5261,6 +6869,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>7287700</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>19382</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5307,6 +6931,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>7387800</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>20296</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5353,6 +6993,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>4599700</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>22771</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5399,6 +7055,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>4500300</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>21533</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5445,6 +7117,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>9948000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>19168</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5495,6 +7183,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5541,6 +7249,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>6599000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>18331</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5587,6 +7311,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>6557000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>18214</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5633,6 +7373,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>6671000</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>18952</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5679,6 +7435,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>7188000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>20248</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5725,6 +7497,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>7122000</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>18941</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5771,6 +7559,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>7188000</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>19747</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5817,6 +7621,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>4500300</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>22279</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5863,6 +7683,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>4400200</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>21054</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5909,6 +7745,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>9822000</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>18888</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5939,7 +7791,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -5955,6 +7807,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>9188200</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>21269</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6001,6 +7869,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>6385000</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>18724</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6047,6 +7931,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>6548000</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>18189</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6093,6 +7993,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>6505000</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>18069</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6139,6 +8055,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>6599000</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>18747</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6185,6 +8117,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>6918000</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>19487</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6231,6 +8179,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>7287700</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>19382</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6277,6 +8241,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>7188000</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>19747</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6323,6 +8303,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>4500300</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>22279</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6369,6 +8365,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>4288000</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>20517</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6415,6 +8427,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>9495000</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>18260</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6445,7 +8473,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -6461,6 +8489,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>8988000</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>20806</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6507,6 +8551,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>6314000</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>18516</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6553,6 +8613,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>6476000</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>17989</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6599,6 +8675,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>6434000</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>17872</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6645,6 +8737,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>6528000</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>18545</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6691,6 +8799,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>6847000</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>19287</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6737,6 +8861,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>7088000</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>18851</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6783,6 +8923,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>6881000</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>18904</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6829,6 +8985,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>4500300</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>22279</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6875,6 +9047,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>4288000</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>20517</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6921,6 +9109,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>9414000</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>18104</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6951,7 +9155,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -6967,6 +9171,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>8887900</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>20574</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7013,6 +9233,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>6242000</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>18305</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7059,6 +9295,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>6429000</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>17858</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7105,6 +9357,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>6361000</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>17669</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7151,6 +9419,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>6480000</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>18409</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7197,6 +9481,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>6776000</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>19087</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7243,6 +9543,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>7088200</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>18852</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7289,6 +9605,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>6825000</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>18750</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7335,6 +9667,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>4400200</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>21783</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7381,6 +9729,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>4288000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>20517</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7427,6 +9791,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>9342000</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>17965</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7473,6 +9853,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>8489000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>19650</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7519,6 +9915,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>6169000</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>18091</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7565,6 +9977,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>6357000</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>17658</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7611,6 +10039,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>6289000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>17469</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7657,6 +10101,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>6408000</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>18205</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7703,6 +10163,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>6705000</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>18887</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7749,6 +10225,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>7088200</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>18852</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7795,6 +10287,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>6769000</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>18596</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7841,6 +10349,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>20792</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7887,6 +10411,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>4088000</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>19560</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7933,6 +10473,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>9688000</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>18631</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7979,6 +10535,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>8365000</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>19363</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8025,6 +10597,22 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>6097000</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>17880</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8071,6 +10659,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>6285000</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>17458</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8117,6 +10721,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>6218000</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>17272</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8163,6 +10783,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>6337000</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>18003</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8209,6 +10845,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>6634000</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>18687</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8255,6 +10907,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>6896000</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>18340</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8301,6 +10969,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>6739000</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>18514</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8347,6 +11031,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>4088000</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>20238</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8393,6 +11093,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>3988000</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>19081</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8439,6 +11155,22 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>8988000</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>17285</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8485,6 +11217,22 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>8288000</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>19185</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8531,6 +11279,22 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>6026000</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>17672</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8577,6 +11341,22 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>6213000</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>17258</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8623,6 +11403,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>6146000</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>17072</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8669,6 +11465,22 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>6264000</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>17795</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8715,6 +11527,22 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>6563000</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>18487</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8761,6 +11589,22 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>6988100</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>18585</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8807,6 +11651,22 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>6683000</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>18360</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8853,6 +11713,22 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>4088000</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>20238</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8899,6 +11775,22 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>3988000</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>19081</v>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8949,6 +11841,26 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8999,6 +11911,26 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9045,6 +11977,22 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>5954000</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>17460</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9091,6 +12039,22 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>6141000</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>17058</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9137,6 +12101,22 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>6073000</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>16869</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9183,6 +12163,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>6192000</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>17591</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9229,6 +12225,22 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>6588000</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>18558</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9275,6 +12287,22 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>6988100</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>18585</v>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9325,6 +12353,26 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9371,6 +12419,22 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>4300100</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>21500</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>薈淳現樓付款計劃</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9417,6 +12481,22 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>3988000</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>19081</v>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9467,6 +12547,26 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9513,6 +12613,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>5881000</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>17246</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9559,6 +12675,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>6069000</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>16858</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9605,6 +12737,22 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>5788000</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>16078</v>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9651,6 +12799,22 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>6121000</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>17389</v>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9697,6 +12861,22 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>6588000</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>18558</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9747,13 +12927,33 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -9830,12 +13030,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -9977,7 +13177,7 @@
           <t>J | 209呎 (开放式)
 $671万
 $32,124/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
@@ -9985,7 +13185,7 @@
           <t>K | 202呎 (开放式)
 $700万
 $34,653/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L5" s="20" t="inlineStr">
@@ -10008,10 +13208,10 @@
           <t>A | 376呎 (2房)
 $1155万
 $30,729/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $1098万
@@ -10019,7 +13219,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $1055万
@@ -10027,12 +13227,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>D | 356呎 (2房)
 $709万
 $19,910/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -10040,7 +13240,7 @@
           <t>E | 468呎 (3房)
 $1455万
 $31,098/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr"/>
@@ -10058,10 +13258,98 @@
           <t>J | 209呎 (开放式)
 $657万
 $31,440/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>K | 202呎 (开放式)
+$686万
+$33,946/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>L | 364呎 (2房)
+$1155万
+$31,742/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 376呎 (2房)
+$1127万
+$29,971/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 355呎 (2房)
+$1084万
+$30,535/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 352呎 (2房)
+$1055万
+$29,983/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 360呎 (2房)
+$699万
+$19,411/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>E | 360呎 (2房)
+$701万
+$19,469/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 462呎 (3房)
+$1555万
+$33,667/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr"/>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>H | 520呎 (3房)
+$1678万
+$32,275/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J7" s="24" t="inlineStr">
+        <is>
+          <t>J | 209呎 (开放式)
+$657万
+$31,440/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K7" s="24" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $686万
@@ -10069,30 +13357,30 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
-$1155万
-$31,742/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
+$1127万
+$30,959/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $1127万
 $29,971/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $1084万
@@ -10100,48 +13388,48 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
-$1055万
-$29,983/呎
+$1041万
+$29,577/呎
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $699万
 $19,411/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F7" s="24" t="inlineStr">
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
-$701万
-$19,469/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G7" s="22" t="inlineStr">
+$709万
+$19,689/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
 $1555万
 $33,667/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr"/>
-      <c r="I7" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr"/>
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
-$1678万
-$32,275/呎
+$1653万
+$31,781/呎
 (在售)</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="J8" s="24" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $657万
@@ -10149,7 +13437,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K8" s="24" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $686万
@@ -10157,38 +13445,38 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L7" s="22" t="inlineStr">
+      <c r="L8" s="22" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $1127万
 $30,959/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
-$1127万
-$29,971/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
+$1113万
+$29,590/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
-$1084万
-$30,535/呎
+$1070万
+$30,132/呎
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $1041万
@@ -10196,40 +13484,40 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $699万
 $19,411/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $709万
 $19,689/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G8" s="22" t="inlineStr">
+(26年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
-$1555万
-$33,667/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr"/>
-      <c r="I8" s="22" t="inlineStr">
+$1498万
+$32,431/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr"/>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
-$1653万
-$31,781/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="inlineStr">
+$1627万
+$31,287/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J9" s="24" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $657万
@@ -10237,95 +13525,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr">
-        <is>
-          <t>K | 202呎 (开放式)
-$686万
-$33,946/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L8" s="22" t="inlineStr">
-        <is>
-          <t>L | 364呎 (2房)
-$1127万
-$30,959/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>A | 376呎 (2房)
-$1113万
-$29,590/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>B | 355呎 (2房)
-$1070万
-$30,132/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>C | 352呎 (2房)
-$1041万
-$29,577/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>D | 360呎 (2房)
-$699万
-$19,411/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>E | 360呎 (2房)
-$709万
-$19,689/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>F | 462呎 (3房)
-$1498万
-$32,431/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr"/>
-      <c r="I9" s="22" t="inlineStr">
-        <is>
-          <t>H | 520呎 (3房)
-$1627万
-$31,287/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="inlineStr">
-        <is>
-          <t>J | 209呎 (开放式)
-$657万
-$31,440/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $671万
@@ -10333,7 +13533,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L9" s="23" t="inlineStr">
+      <c r="L9" s="22" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $1098万
@@ -10353,18 +13553,18 @@
           <t>A | 376呎 (2房)
 $1113万
 $29,590/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $726万
 $20,445/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
+(26年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $1013万
@@ -10372,12 +13572,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $681万
 $18,925/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -10385,10 +13585,10 @@
           <t>E | 360呎 (2房)
 $1027万
 $28,525/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
 $1484万
@@ -10402,18 +13602,18 @@
           <t>H | 520呎 (3房)
 $1601万
 $30,790/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J10" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $450万
 $21,531/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="inlineStr">
+(26年-06月-18日)</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $671万
@@ -10421,7 +13621,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L10" s="23" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $1098万
@@ -10436,15 +13636,15 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $737万
 $19,596/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $1041万
@@ -10452,7 +13652,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $1013万
@@ -10460,32 +13660,32 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $689万
 $19,133/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $699万
 $19,411/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
+(26年-05月-31日)</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
 $999万
 $21,619/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr"/>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $1575万
@@ -10493,7 +13693,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J11" s="23" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $643万
@@ -10501,7 +13701,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $671万
@@ -10509,7 +13709,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L11" s="23" t="inlineStr">
+      <c r="L11" s="22" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $1070万
@@ -10524,15 +13724,15 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $737万
 $19,596/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $1041万
@@ -10540,23 +13740,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $699万
 $19,852/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $689万
 $19,133/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $998万
@@ -10564,7 +13764,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
 $1470万
@@ -10573,7 +13773,7 @@
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr"/>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $1570万
@@ -10581,7 +13781,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J12" s="23" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $655万
@@ -10589,7 +13789,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="24" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $657万
@@ -10597,7 +13797,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L12" s="23" t="inlineStr">
+      <c r="L12" s="22" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $1070万
@@ -10612,15 +13812,15 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $720万
 $19,136/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $1041万
@@ -10628,7 +13828,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $998万
@@ -10636,23 +13836,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $666万
 $18,500/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $670万
 $18,617/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
 $1441万
@@ -10666,10 +13866,10 @@
           <t>H | 520呎 (3房)
 $1524万
 $29,308/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $643万
@@ -10677,20 +13877,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K13" s="24" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $460万
 $22,772/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L13" s="24" t="inlineStr">
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $724万
 $19,904/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -10700,7 +13900,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $1041万
@@ -10708,39 +13908,39 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $706万
 $19,887/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $674万
 $19,156/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $661万
 $18,356/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $665万
 $18,475/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
+(26年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 462呎 (3房)
 $1427万
@@ -10749,7 +13949,7 @@
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr"/>
-      <c r="I14" s="23" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $1498万
@@ -10757,15 +13957,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J14" s="24" t="inlineStr">
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $440万
 $21,053/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="K14" s="23" t="inlineStr">
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $657万
@@ -10773,12 +13973,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $729万
 $20,022/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -10788,44 +13988,44 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $712万
 $18,941/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $719万
 $20,248/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $667万
 $18,952/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $656万
 $18,214/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
+(26年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $660万
 $18,331/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -10837,15 +14037,15 @@
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr"/>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>H | 519呎 (3房)
 $995万
 $19,168/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J15" s="23" t="inlineStr">
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $643万
@@ -10853,7 +14053,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="24" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $657万
@@ -10861,7 +14061,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L15" s="23" t="inlineStr">
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $1055万
@@ -10876,7 +14076,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $1041万
@@ -10884,44 +14084,44 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $692万
 $19,487/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
+(26年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $660万
 $18,747/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $650万
 $18,069/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
+(26年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $655万
 $18,189/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $638万
 $18,724/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -10929,18 +14129,18 @@
           <t>G | 432呎 (3房)
 $1313万
 $30,384/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $982万
 $18,888/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J16" s="23" t="inlineStr">
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $629万
@@ -10948,7 +14148,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K16" s="23" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $643万
@@ -10956,12 +14156,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="23" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $719万
 $19,747/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -10971,52 +14171,52 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $709万
 $18,851/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $685万
 $19,287/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $653万
 $18,545/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $643万
 $17,872/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $648万
 $17,989/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $631万
 $18,516/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -11024,26 +14224,26 @@
           <t>G | 432呎 (3房)
 $1284万
 $29,722/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $950万
 $18,260/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J17" s="24" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $429万
 $20,517/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K17" s="23" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $643万
@@ -11051,12 +14251,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $719万
 $19,747/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -11066,7 +14266,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $1013万
@@ -11074,44 +14274,44 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $678万
 $19,087/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $648万
 $18,409/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $636万
 $17,669/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $643万
 $17,858/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $624万
 $18,305/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -11119,26 +14319,26 @@
           <t>G | 432呎 (3房)
 $1270万
 $29,391/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $941万
 $18,104/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J18" s="24" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $429万
 $20,517/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K18" s="22" t="inlineStr">
+(26年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="K18" s="24" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $643万
@@ -11146,12 +14346,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $688万
 $18,904/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -11161,7 +14361,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $1013万
@@ -11169,71 +14369,71 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $670万
 $18,887/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $641万
 $18,205/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $629万
 $17,469/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $636万
 $17,658/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G19" s="24" t="inlineStr">
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $617万
 $18,091/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H19" s="24" t="inlineStr">
+(26年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>G | 432呎 (3房)
 $849万
 $19,650/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $934万
 $17,965/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="inlineStr">
+(26年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $429万
 $20,517/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K19" s="23" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $629万
@@ -11241,12 +14441,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $682万
 $18,750/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -11256,63 +14456,63 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $690万
 $18,340/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $663万
 $18,687/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $634万
 $18,003/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
+(26年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $622万
 $17,272/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F20" s="24" t="inlineStr">
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $628万
 $17,458/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G20" s="24" t="inlineStr">
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $610万
 $17,880/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H20" s="24" t="inlineStr">
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>G | 432呎 (3房)
 $836万
 $19,363/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $1384万
@@ -11320,28 +14520,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J20" s="24" t="inlineStr">
+      <c r="J20" s="23" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $409万
 $19,560/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K20" s="24" t="inlineStr">
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $420万
 $20,792/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L20" s="24" t="inlineStr">
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $677万
 $18,596/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -11351,7 +14551,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $998万
@@ -11359,47 +14559,47 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $656万
 $18,487/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $626万
 $17,795/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
+(26年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $615万
 $17,072/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $621万
 $17,258/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $603万
 $17,672/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H21" s="23" t="inlineStr">
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>G | 432呎 (3房)
 $1184万
@@ -11407,36 +14607,36 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I21" s="24" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>H | 520呎 (3房)
 $899万
 $17,285/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J21" s="24" t="inlineStr">
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $399万
 $19,081/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K21" s="24" t="inlineStr">
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $409万
 $20,238/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L21" s="24" t="inlineStr">
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $674万
 $18,514/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -11446,7 +14646,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 376呎 (2房)
 $998万
@@ -11454,44 +14654,44 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $659万
 $18,558/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $619万
 $17,591/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $607万
 $16,869/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $614万
 $17,058/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $595万
 $17,460/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -11510,28 +14710,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J22" s="24" t="inlineStr">
+      <c r="J22" s="23" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $399万
 $19,081/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K22" s="24" t="inlineStr">
+(26年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
         <is>
           <t>K | 202呎 (开放式)
 $409万
 $20,238/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L22" s="24" t="inlineStr">
+(26年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
         <is>
           <t>L | 364呎 (2房)
 $668万
 $18,360/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -11549,44 +14749,44 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 355呎 (2房)
 $659万
 $18,558/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 352呎 (2房)
 $612万
 $17,389/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 360呎 (2房)
 $579万
 $16,078/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 360呎 (2房)
 $607万
 $16,858/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G23" s="24" t="inlineStr">
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $588万
 $17,246/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -11598,15 +14798,15 @@
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr"/>
-      <c r="J23" s="24" t="inlineStr">
+      <c r="J23" s="23" t="inlineStr">
         <is>
           <t>J | 209呎 (开放式)
 $399万
 $19,081/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K23" s="23" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>K | 200呎 (开放式)
 $614万
